--- a/branches/master/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/master/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-27T13:30:57+00:00</t>
+    <t>2023-04-28T11:34:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/master/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T11:34:44+00:00</t>
+    <t>2023-04-30T04:59:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/master/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T04:59:44+00:00</t>
+    <t>2023-05-01T18:23:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/master/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T18:23:44+00:00</t>
+    <t>2023-05-03T04:38:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/master/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-03T04:38:57+00:00</t>
+    <t>2023-05-04T06:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/master/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T06:27:52+00:00</t>
+    <t>2023-05-05T18:22:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/master/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T18:22:20+00:00</t>
+    <t>2023-05-05T18:27:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/master/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T18:27:53+00:00</t>
+    <t>2023-05-05T20:52:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/master/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T20:52:16+00:00</t>
+    <t>2023-05-06T12:19:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/master/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-06T12:19:14+00:00</t>
+    <t>2023-05-07T12:14:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/master/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:14:35+00:00</t>
+    <t>2023-05-07T13:36:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/master/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T13:36:00+00:00</t>
+    <t>2023-05-08T07:05:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -5755,7 +5755,7 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>86</v>

--- a/branches/master/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/master/StructureDefinition-hiv-lab-task.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$93</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$94</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3390" uniqueCount="590">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3424" uniqueCount="597">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T07:05:14+00:00</t>
+    <t>2023-05-08T20:00:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -421,33 +421,57 @@
     <t>Task.extension</t>
   </si>
   <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>Task.extension:ResultStatusIndex</t>
+  </si>
+  <si>
+    <t>ResultStatusIndex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://openhie.org/fhir/rwanda-hiv/StructureDefinition/result-status-index}
+</t>
+  </si>
+  <si>
+    <t>Result Status Index</t>
+  </si>
+  <si>
+    <t>The result status index.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>Task.modifierExtension</t>
+  </si>
+  <si>
     <t>extensions
 user content</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>Task.modifierExtension</t>
-  </si>
-  <si>
     <t>Extensions that cannot be ignored</t>
   </si>
   <si>
@@ -455,6 +479,9 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
@@ -527,17 +554,13 @@
     <t>Task.identifier.extension</t>
   </si>
   <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
     <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
   </si>
   <si>
     <t>Element.extension</t>
@@ -852,7 +875,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/lab-integration/order-id</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/lab-integration/order-number</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -2154,12 +2177,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN93"/>
+  <dimension ref="A1:AN94"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="42.2890625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="38.03515625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="15.40625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="17.7109375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -3123,7 +3146,7 @@
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -3142,17 +3165,15 @@
         <v>77</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>132</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>133</v>
       </c>
-      <c r="M9" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>135</v>
-      </c>
+      <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>77</v>
@@ -3189,16 +3210,14 @@
         <v>77</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="AF9" t="s" s="2">
         <v>136</v>
@@ -3219,7 +3238,7 @@
         <v>77</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>129</v>
+        <v>77</v>
       </c>
       <c r="AM9" t="s" s="2">
         <v>77</v>
@@ -3233,43 +3252,41 @@
         <v>138</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="C10" s="2"/>
+        <v>130</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="D10" t="s" s="2">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>141</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>77</v>
       </c>
@@ -3317,7 +3334,7 @@
         <v>77</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -3326,7 +3343,7 @@
         <v>79</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>77</v>
+        <v>143</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>137</v>
@@ -3335,7 +3352,7 @@
         <v>77</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>129</v>
+        <v>77</v>
       </c>
       <c r="AM10" t="s" s="2">
         <v>77</v>
@@ -3346,18 +3363,18 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>77</v>
+        <v>145</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="G11" t="s" s="2">
         <v>79</v>
@@ -3366,22 +3383,26 @@
         <v>77</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="J11" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
+        <v>147</v>
+      </c>
+      <c r="N11" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="O11" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="P11" t="s" s="2">
         <v>77</v>
       </c>
@@ -3417,19 +3438,19 @@
         <v>77</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>147</v>
+        <v>77</v>
       </c>
       <c r="AC11" t="s" s="2">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="AD11" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>149</v>
+        <v>77</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -3441,16 +3462,16 @@
         <v>77</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>150</v>
+        <v>77</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>151</v>
+        <v>129</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>152</v>
+        <v>77</v>
       </c>
       <c r="AN11" t="s" s="2">
         <v>77</v>
@@ -3458,14 +3479,12 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="C12" t="s" s="2">
-        <v>154</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
         <v>77</v>
       </c>
@@ -3474,7 +3493,7 @@
         <v>86</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>77</v>
@@ -3486,13 +3505,13 @@
         <v>77</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -3531,19 +3550,19 @@
         <v>77</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>77</v>
+        <v>156</v>
       </c>
       <c r="AD12" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>77</v>
+        <v>157</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -3558,13 +3577,13 @@
         <v>98</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>77</v>
@@ -3572,18 +3591,20 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="C13" s="2"/>
+        <v>151</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>162</v>
+      </c>
       <c r="D13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="G13" t="s" s="2">
         <v>86</v>
@@ -3598,13 +3619,13 @@
         <v>77</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3655,28 +3676,28 @@
         <v>77</v>
       </c>
       <c r="AF13" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AG13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH13" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ13" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK13" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="AL13" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="AM13" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AG13" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH13" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL13" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>77</v>
@@ -3684,21 +3705,21 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>77</v>
@@ -3710,17 +3731,15 @@
         <v>77</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>132</v>
+        <v>165</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>133</v>
+        <v>166</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>135</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>77</v>
@@ -3757,16 +3776,16 @@
         <v>77</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AD14" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>167</v>
+        <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
         <v>168</v>
@@ -3775,19 +3794,19 @@
         <v>78</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>137</v>
+        <v>77</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>77</v>
@@ -3798,46 +3817,44 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>77</v>
+        <v>145</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>174</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>77</v>
       </c>
@@ -3861,63 +3878,63 @@
         <v>77</v>
       </c>
       <c r="X15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AF15" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="Y15" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="Z15" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>178</v>
-      </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>129</v>
+        <v>77</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3934,25 +3951,25 @@
         <v>77</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="J16" t="s" s="2">
         <v>87</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>182</v>
+        <v>106</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>77</v>
@@ -3977,13 +3994,13 @@
         <v>77</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>77</v>
@@ -4001,7 +4018,7 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -4019,21 +4036,21 @@
         <v>77</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>191</v>
+        <v>129</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4053,19 +4070,23 @@
         <v>77</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>157</v>
+        <v>189</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>158</v>
+        <v>190</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="N17" s="2"/>
-      <c r="O17" s="2"/>
+        <v>191</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="O17" t="s" s="2">
+        <v>193</v>
+      </c>
       <c r="P17" t="s" s="2">
         <v>77</v>
       </c>
@@ -4089,13 +4110,13 @@
         <v>77</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>77</v>
+        <v>194</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>77</v>
+        <v>195</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>77</v>
+        <v>196</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>77</v>
@@ -4113,7 +4134,7 @@
         <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>160</v>
+        <v>197</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -4125,38 +4146,38 @@
         <v>77</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>161</v>
+        <v>186</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>77</v>
+        <v>198</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>77</v>
@@ -4168,17 +4189,15 @@
         <v>77</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>132</v>
+        <v>165</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>133</v>
+        <v>166</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>135</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>77</v>
@@ -4215,16 +4234,16 @@
         <v>77</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>167</v>
+        <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
         <v>168</v>
@@ -4233,19 +4252,19 @@
         <v>78</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>137</v>
+        <v>77</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>77</v>
@@ -4256,14 +4275,14 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>77</v>
+        <v>145</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -4279,23 +4298,21 @@
         <v>77</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>198</v>
+        <v>131</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>199</v>
+        <v>172</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>202</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>77</v>
       </c>
@@ -4331,19 +4348,19 @@
         <v>77</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>77</v>
+        <v>134</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>77</v>
+        <v>174</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>203</v>
+        <v>175</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -4355,27 +4372,27 @@
         <v>77</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>204</v>
+        <v>169</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>205</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4386,7 +4403,7 @@
         <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>77</v>
@@ -4395,19 +4412,23 @@
         <v>77</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>157</v>
+        <v>205</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>158</v>
+        <v>206</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
+        <v>207</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="O20" t="s" s="2">
+        <v>209</v>
+      </c>
       <c r="P20" t="s" s="2">
         <v>77</v>
       </c>
@@ -4455,50 +4476,50 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>160</v>
+        <v>210</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>161</v>
+        <v>211</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>77</v>
+        <v>212</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>77</v>
@@ -4510,17 +4531,15 @@
         <v>77</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>132</v>
+        <v>165</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>133</v>
+        <v>166</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>135</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>77</v>
@@ -4557,16 +4576,16 @@
         <v>77</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>167</v>
+        <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
         <v>168</v>
@@ -4575,19 +4594,19 @@
         <v>78</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>137</v>
+        <v>77</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>77</v>
@@ -4598,21 +4617,21 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>77</v>
+        <v>145</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>77</v>
@@ -4621,23 +4640,21 @@
         <v>77</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>100</v>
+        <v>131</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>212</v>
+        <v>172</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>213</v>
+        <v>173</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>215</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>77</v>
       </c>
@@ -4646,7 +4663,7 @@
         <v>77</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>216</v>
+        <v>77</v>
       </c>
       <c r="T22" t="s" s="2">
         <v>77</v>
@@ -4673,51 +4690,51 @@
         <v>77</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>77</v>
+        <v>134</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>77</v>
+        <v>174</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>217</v>
+        <v>175</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>218</v>
+        <v>169</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>219</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4740,18 +4757,20 @@
         <v>87</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>157</v>
+        <v>100</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="M23" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="O23" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="M23" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>77</v>
       </c>
@@ -4760,7 +4779,7 @@
         <v>77</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>77</v>
+        <v>223</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>77</v>
@@ -4799,7 +4818,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4817,21 +4836,21 @@
         <v>77</v>
       </c>
       <c r="AL23" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AM23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN23" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>227</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="B24" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="B24" t="s" s="2">
-        <v>229</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4854,18 +4873,18 @@
         <v>87</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>106</v>
+        <v>165</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="N24" s="2"/>
-      <c r="O24" t="s" s="2">
-        <v>232</v>
-      </c>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>77</v>
       </c>
@@ -4874,7 +4893,7 @@
         <v>77</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>154</v>
+        <v>77</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>77</v>
@@ -4913,7 +4932,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4931,21 +4950,21 @@
         <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="AM24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN24" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>235</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="B25" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="B25" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4968,17 +4987,17 @@
         <v>87</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>157</v>
+        <v>106</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>238</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>239</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -4988,7 +5007,7 @@
         <v>77</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>241</v>
+        <v>162</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>77</v>
@@ -5027,7 +5046,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -5045,21 +5064,21 @@
         <v>77</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5082,19 +5101,17 @@
         <v>87</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="N26" s="2"/>
+      <c r="O26" t="s" s="2">
         <v>247</v>
-      </c>
-      <c r="L26" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>251</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>77</v>
@@ -5104,7 +5121,7 @@
         <v>77</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>77</v>
+        <v>248</v>
       </c>
       <c r="T26" t="s" s="2">
         <v>77</v>
@@ -5143,7 +5160,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -5161,21 +5178,21 @@
         <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>254</v>
+        <v>251</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5198,19 +5215,19 @@
         <v>87</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>157</v>
+        <v>254</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="N27" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>258</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>260</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -5220,7 +5237,7 @@
         <v>77</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>261</v>
+        <v>77</v>
       </c>
       <c r="T27" t="s" s="2">
         <v>77</v>
@@ -5259,7 +5276,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -5277,21 +5294,21 @@
         <v>77</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>264</v>
+        <v>261</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5299,7 +5316,7 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>86</v>
@@ -5314,32 +5331,32 @@
         <v>87</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>100</v>
+        <v>165</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="M28" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="O28" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>270</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
-        <v>271</v>
+        <v>77</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>77</v>
+        <v>268</v>
       </c>
       <c r="T28" t="s" s="2">
-        <v>272</v>
+        <v>77</v>
       </c>
       <c r="U28" t="s" s="2">
         <v>77</v>
@@ -5375,7 +5392,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -5393,21 +5410,21 @@
         <v>77</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>275</v>
+        <v>271</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5430,30 +5447,32 @@
         <v>87</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>157</v>
+        <v>100</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="O29" s="2"/>
+        <v>276</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>277</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q29" s="2"/>
       <c r="R29" t="s" s="2">
-        <v>77</v>
+        <v>278</v>
       </c>
       <c r="S29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="T29" t="s" s="2">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="U29" t="s" s="2">
         <v>77</v>
@@ -5489,7 +5508,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5507,21 +5526,21 @@
         <v>77</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5529,7 +5548,7 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>86</v>
@@ -5544,15 +5563,17 @@
         <v>87</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="N30" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="L30" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>77</v>
@@ -5565,7 +5586,7 @@
         <v>77</v>
       </c>
       <c r="T30" t="s" s="2">
-        <v>77</v>
+        <v>288</v>
       </c>
       <c r="U30" t="s" s="2">
         <v>77</v>
@@ -5601,7 +5622,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5619,21 +5640,21 @@
         <v>77</v>
       </c>
       <c r="AL30" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="AM30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN30" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>292</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="B31" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="B31" t="s" s="2">
-        <v>294</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5656,17 +5677,15 @@
         <v>87</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="M31" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>298</v>
-      </c>
+      <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>77</v>
@@ -5715,7 +5734,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5733,21 +5752,21 @@
         <v>77</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5755,7 +5774,7 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>86</v>
@@ -5770,18 +5789,18 @@
         <v>87</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="N32" s="2"/>
-      <c r="O32" t="s" s="2">
-        <v>306</v>
-      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>77</v>
       </c>
@@ -5829,7 +5848,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5844,16 +5863,16 @@
         <v>98</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL32" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="AL32" t="s" s="2">
+      <c r="AM32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN32" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>77</v>
       </c>
     </row>
     <row r="33" hidden="true">
@@ -5869,7 +5888,7 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>86</v>
@@ -5884,17 +5903,17 @@
         <v>87</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>100</v>
+        <v>310</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>77</v>
@@ -5958,10 +5977,10 @@
         <v>98</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>77</v>
@@ -5972,10 +5991,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5986,7 +6005,7 @@
         <v>78</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>77</v>
@@ -5998,16 +6017,18 @@
         <v>87</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>314</v>
+        <v>100</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
+      <c r="O34" t="s" s="2">
+        <v>318</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>77</v>
       </c>
@@ -6055,13 +6076,13 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>77</v>
@@ -6070,10 +6091,10 @@
         <v>98</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>77</v>
@@ -6084,10 +6105,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6098,7 +6119,7 @@
         <v>78</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>77</v>
@@ -6110,18 +6131,16 @@
         <v>87</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>144</v>
+        <v>321</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="N35" s="2"/>
-      <c r="O35" t="s" s="2">
-        <v>322</v>
-      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>77</v>
       </c>
@@ -6169,13 +6188,13 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>77</v>
@@ -6184,10 +6203,10 @@
         <v>98</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>77</v>
@@ -6198,10 +6217,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6212,7 +6231,7 @@
         <v>78</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>77</v>
@@ -6224,7 +6243,7 @@
         <v>87</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>326</v>
+        <v>152</v>
       </c>
       <c r="L36" t="s" s="2">
         <v>327</v>
@@ -6232,11 +6251,9 @@
       <c r="M36" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="N36" t="s" s="2">
+      <c r="N36" s="2"/>
+      <c r="O36" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>330</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -6285,13 +6302,13 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>77</v>
@@ -6300,10 +6317,10 @@
         <v>98</v>
       </c>
       <c r="AK36" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="AL36" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="AL36" t="s" s="2">
-        <v>332</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>77</v>
@@ -6314,10 +6331,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6325,22 +6342,22 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="J37" t="s" s="2">
         <v>87</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>106</v>
+        <v>333</v>
       </c>
       <c r="L37" t="s" s="2">
         <v>334</v>
@@ -6348,9 +6365,11 @@
       <c r="M37" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="N37" s="2"/>
+      <c r="N37" t="s" s="2">
+        <v>336</v>
+      </c>
       <c r="O37" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>77</v>
@@ -6375,13 +6394,13 @@
         <v>77</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>175</v>
+        <v>77</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>335</v>
+        <v>77</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>337</v>
+        <v>77</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>77</v>
@@ -6399,13 +6418,13 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>77</v>
@@ -6420,7 +6439,7 @@
         <v>339</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>340</v>
+        <v>77</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>77</v>
@@ -6428,10 +6447,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6439,7 +6458,7 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>86</v>
@@ -6448,24 +6467,24 @@
         <v>77</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="J38" t="s" s="2">
         <v>87</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>182</v>
+        <v>106</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" s="2"/>
+      <c r="O38" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="N38" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>77</v>
       </c>
@@ -6489,11 +6508,13 @@
         <v>77</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="Y38" s="2"/>
+        <v>182</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>342</v>
+      </c>
       <c r="Z38" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>77</v>
@@ -6511,10 +6532,10 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>86</v>
@@ -6526,13 +6547,13 @@
         <v>98</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>77</v>
+        <v>345</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>346</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>77</v>
+        <v>347</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>77</v>
@@ -6540,10 +6561,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6557,24 +6578,26 @@
         <v>86</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>157</v>
+        <v>189</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>158</v>
+        <v>349</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>350</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>351</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>77</v>
@@ -6599,13 +6622,11 @@
         <v>77</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y39" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="Y39" s="2"/>
       <c r="Z39" t="s" s="2">
-        <v>77</v>
+        <v>352</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>77</v>
@@ -6623,7 +6644,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>160</v>
+        <v>348</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6635,13 +6656,13 @@
         <v>77</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>161</v>
+        <v>353</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>77</v>
@@ -6652,21 +6673,21 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>77</v>
@@ -6678,17 +6699,15 @@
         <v>77</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>132</v>
+        <v>165</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>133</v>
+        <v>166</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>135</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>77</v>
@@ -6725,16 +6744,16 @@
         <v>77</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>167</v>
+        <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
         <v>168</v>
@@ -6743,19 +6762,19 @@
         <v>78</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>137</v>
+        <v>77</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>77</v>
@@ -6766,14 +6785,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>77</v>
+        <v>145</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6789,23 +6808,21 @@
         <v>77</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>198</v>
+        <v>131</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>199</v>
+        <v>172</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>202</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>77</v>
       </c>
@@ -6841,19 +6858,19 @@
         <v>77</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>77</v>
+        <v>134</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>77</v>
+        <v>174</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>203</v>
+        <v>175</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6865,27 +6882,27 @@
         <v>77</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>204</v>
+        <v>169</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>205</v>
+        <v>77</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6896,7 +6913,7 @@
         <v>78</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>77</v>
@@ -6908,19 +6925,19 @@
         <v>87</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>157</v>
+        <v>205</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>257</v>
+        <v>206</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>258</v>
+        <v>207</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>259</v>
+        <v>208</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>260</v>
+        <v>209</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>77</v>
@@ -6930,7 +6947,7 @@
         <v>77</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>351</v>
+        <v>77</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>77</v>
@@ -6969,13 +6986,13 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>262</v>
+        <v>210</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>77</v>
@@ -6987,21 +7004,21 @@
         <v>77</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>263</v>
+        <v>211</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>264</v>
+        <v>212</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7024,17 +7041,19 @@
         <v>87</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>182</v>
+        <v>165</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>353</v>
+        <v>264</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>265</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>266</v>
+      </c>
       <c r="O43" t="s" s="2">
-        <v>355</v>
+        <v>267</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>77</v>
@@ -7044,7 +7063,7 @@
         <v>77</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>77</v>
+        <v>358</v>
       </c>
       <c r="T43" t="s" s="2">
         <v>77</v>
@@ -7059,10 +7078,10 @@
         <v>77</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>356</v>
+        <v>77</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>357</v>
+        <v>77</v>
       </c>
       <c r="Z43" t="s" s="2">
         <v>77</v>
@@ -7083,7 +7102,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>352</v>
+        <v>269</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -7101,13 +7120,13 @@
         <v>77</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>358</v>
+        <v>270</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>77</v>
+        <v>271</v>
       </c>
     </row>
     <row r="44" hidden="true">
@@ -7123,7 +7142,7 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>86</v>
@@ -7138,7 +7157,7 @@
         <v>87</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>106</v>
+        <v>189</v>
       </c>
       <c r="L44" t="s" s="2">
         <v>360</v>
@@ -7146,10 +7165,10 @@
       <c r="M44" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="N44" t="s" s="2">
+      <c r="N44" s="2"/>
+      <c r="O44" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>77</v>
       </c>
@@ -7158,28 +7177,28 @@
         <v>77</v>
       </c>
       <c r="S44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X44" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="T44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X44" t="s" s="2">
-        <v>175</v>
       </c>
       <c r="Y44" t="s" s="2">
         <v>364</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>365</v>
+        <v>77</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>77</v>
@@ -7200,7 +7219,7 @@
         <v>359</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>86</v>
@@ -7212,13 +7231,13 @@
         <v>98</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>366</v>
+        <v>77</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>368</v>
+        <v>77</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>77</v>
@@ -7226,10 +7245,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7237,7 +7256,7 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>86</v>
@@ -7249,54 +7268,52 @@
         <v>77</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="K45" t="s" s="2">
         <v>106</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="O45" s="2"/>
+      <c r="P45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q45" s="2"/>
+      <c r="R45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S45" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="T45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X45" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="Y45" t="s" s="2">
         <v>371</v>
       </c>
-      <c r="N45" s="2"/>
-      <c r="O45" t="s" s="2">
+      <c r="Z45" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="P45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q45" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="R45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X45" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="Y45" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="Z45" t="s" s="2">
-        <v>375</v>
-      </c>
       <c r="AA45" t="s" s="2">
         <v>77</v>
       </c>
@@ -7313,10 +7330,10 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AH45" t="s" s="2">
         <v>86</v>
@@ -7328,13 +7345,13 @@
         <v>98</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>77</v>
@@ -7342,10 +7359,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7365,52 +7382,54 @@
         <v>77</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="P46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q46" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="R46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X46" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="L46" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="M46" t="s" s="2">
+      <c r="Y46" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="N46" t="s" s="2">
+      <c r="Z46" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="O46" s="2"/>
-      <c r="P46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q46" s="2"/>
-      <c r="R46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X46" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="Y46" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="Z46" t="s" s="2">
-        <v>384</v>
-      </c>
       <c r="AA46" t="s" s="2">
         <v>77</v>
       </c>
@@ -7427,7 +7446,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7442,13 +7461,13 @@
         <v>98</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AM46" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="AL46" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>387</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>77</v>
@@ -7456,10 +7475,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7482,15 +7501,17 @@
         <v>87</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>157</v>
+        <v>189</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="N47" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="M47" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>77</v>
@@ -7515,13 +7536,13 @@
         <v>77</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>77</v>
+        <v>363</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>77</v>
+        <v>390</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>77</v>
+        <v>391</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>77</v>
@@ -7539,7 +7560,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7554,13 +7575,13 @@
         <v>98</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>77</v>
+        <v>392</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>77</v>
+        <v>394</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>77</v>
@@ -7568,10 +7589,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7594,20 +7615,16 @@
         <v>87</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>393</v>
+        <v>165</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="O48" t="s" s="2">
         <v>397</v>
       </c>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>77</v>
       </c>
@@ -7655,7 +7672,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7676,7 +7693,7 @@
         <v>398</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>387</v>
+        <v>77</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>77</v>
@@ -7691,7 +7708,7 @@
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>400</v>
+        <v>77</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7710,7 +7727,7 @@
         <v>87</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="L49" t="s" s="2">
         <v>401</v>
@@ -7718,9 +7735,11 @@
       <c r="M49" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="N49" s="2"/>
+      <c r="N49" t="s" s="2">
+        <v>403</v>
+      </c>
       <c r="O49" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>77</v>
@@ -7784,13 +7803,13 @@
         <v>98</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>404</v>
+        <v>77</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>405</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>406</v>
+        <v>394</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>77</v>
@@ -7798,14 +7817,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>77</v>
+        <v>407</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7824,17 +7843,17 @@
         <v>87</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="M50" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>77</v>
@@ -7883,7 +7902,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7898,13 +7917,13 @@
         <v>98</v>
       </c>
       <c r="AK50" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AL50" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="AL50" t="s" s="2">
+      <c r="AM50" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>414</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>77</v>
@@ -7912,10 +7931,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7923,7 +7942,7 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>86</v>
@@ -7938,7 +7957,7 @@
         <v>87</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>287</v>
+        <v>415</v>
       </c>
       <c r="L51" t="s" s="2">
         <v>416</v>
@@ -7947,7 +7966,9 @@
         <v>417</v>
       </c>
       <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
+      <c r="O51" t="s" s="2">
+        <v>418</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>77</v>
       </c>
@@ -7995,7 +8016,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -8010,13 +8031,13 @@
         <v>98</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>77</v>
@@ -8024,14 +8045,14 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>422</v>
+        <v>77</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8041,27 +8062,25 @@
         <v>86</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="M52" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="M52" t="s" s="2">
-        <v>425</v>
-      </c>
       <c r="N52" s="2"/>
-      <c r="O52" t="s" s="2">
-        <v>426</v>
-      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>77</v>
       </c>
@@ -8109,7 +8128,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -8118,19 +8137,19 @@
         <v>86</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>427</v>
+        <v>77</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>77</v>
@@ -8138,14 +8157,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8155,26 +8174,26 @@
         <v>86</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>77</v>
@@ -8223,7 +8242,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8232,19 +8251,19 @@
         <v>86</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>77</v>
+        <v>435</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>436</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>77</v>
+        <v>437</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>77</v>
@@ -8252,24 +8271,24 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>77</v>
+        <v>439</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>86</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>77</v>
@@ -8278,17 +8297,17 @@
         <v>87</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>77</v>
@@ -8337,7 +8356,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8346,19 +8365,19 @@
         <v>86</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>77</v>
+        <v>434</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>442</v>
+        <v>77</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>443</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>444</v>
+        <v>77</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>77</v>
@@ -8366,10 +8385,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8380,7 +8399,7 @@
         <v>78</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>77</v>
@@ -8389,10 +8408,10 @@
         <v>77</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>182</v>
+        <v>445</v>
       </c>
       <c r="L55" t="s" s="2">
         <v>446</v>
@@ -8427,13 +8446,13 @@
         <v>77</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>449</v>
+        <v>77</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>450</v>
+        <v>77</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>77</v>
@@ -8451,13 +8470,13 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>77</v>
@@ -8466,13 +8485,13 @@
         <v>98</v>
       </c>
       <c r="AK55" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AM55" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="AL55" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>77</v>
@@ -8480,45 +8499,43 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>455</v>
+        <v>77</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>456</v>
+        <v>189</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>459</v>
-      </c>
+        <v>454</v>
+      </c>
+      <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>77</v>
@@ -8543,13 +8560,13 @@
         <v>77</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>77</v>
+        <v>456</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>77</v>
+        <v>457</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>77</v>
@@ -8567,13 +8584,13 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>77</v>
@@ -8582,13 +8599,13 @@
         <v>98</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>77</v>
@@ -8596,14 +8613,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>77</v>
+        <v>462</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8622,15 +8639,17 @@
         <v>87</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="L57" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="M57" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
         <v>467</v>
       </c>
@@ -8681,7 +8700,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8702,7 +8721,7 @@
         <v>469</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>77</v>
@@ -8710,10 +8729,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8733,10 +8752,10 @@
         <v>77</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>182</v>
+        <v>471</v>
       </c>
       <c r="L58" t="s" s="2">
         <v>472</v>
@@ -8744,10 +8763,10 @@
       <c r="M58" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="N58" t="s" s="2">
+      <c r="N58" s="2"/>
+      <c r="O58" t="s" s="2">
         <v>474</v>
       </c>
-      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>77</v>
       </c>
@@ -8771,10 +8790,10 @@
         <v>77</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>356</v>
+        <v>77</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>475</v>
+        <v>77</v>
       </c>
       <c r="Z58" t="s" s="2">
         <v>77</v>
@@ -8795,7 +8814,7 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8810,24 +8829,24 @@
         <v>98</v>
       </c>
       <c r="AK58" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AL58" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="AL58" t="s" s="2">
+      <c r="AM58" t="s" s="2">
         <v>477</v>
       </c>
-      <c r="AM58" t="s" s="2">
-        <v>478</v>
-      </c>
       <c r="AN58" t="s" s="2">
-        <v>479</v>
+        <v>77</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8850,16 +8869,16 @@
         <v>77</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>393</v>
+        <v>189</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="M59" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="N59" t="s" s="2">
         <v>481</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>482</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8885,10 +8904,10 @@
         <v>77</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>77</v>
+        <v>363</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>77</v>
+        <v>482</v>
       </c>
       <c r="Z59" t="s" s="2">
         <v>77</v>
@@ -8909,7 +8928,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8930,18 +8949,18 @@
         <v>484</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>77</v>
+        <v>486</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8952,7 +8971,7 @@
         <v>78</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>77</v>
@@ -8964,15 +8983,17 @@
         <v>77</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>486</v>
+        <v>400</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>487</v>
+        <v>479</v>
       </c>
       <c r="M60" t="s" s="2">
         <v>488</v>
       </c>
-      <c r="N60" s="2"/>
+      <c r="N60" t="s" s="2">
+        <v>489</v>
+      </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>77</v>
@@ -9021,13 +9042,13 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>77</v>
@@ -9036,16 +9057,16 @@
         <v>98</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>77</v>
+        <v>485</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>491</v>
+        <v>77</v>
       </c>
     </row>
     <row r="61" hidden="true">
@@ -9067,7 +9088,7 @@
         <v>79</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>77</v>
@@ -9157,19 +9178,19 @@
         <v>77</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>77</v>
+        <v>498</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>499</v>
+        <v>77</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -9179,7 +9200,7 @@
         <v>79</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>77</v>
@@ -9196,9 +9217,7 @@
       <c r="M62" t="s" s="2">
         <v>502</v>
       </c>
-      <c r="N62" t="s" s="2">
-        <v>503</v>
-      </c>
+      <c r="N62" s="2"/>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>77</v>
@@ -9247,7 +9266,7 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -9262,10 +9281,10 @@
         <v>98</v>
       </c>
       <c r="AK62" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="AL62" t="s" s="2">
         <v>504</v>
-      </c>
-      <c r="AL62" t="s" s="2">
-        <v>505</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>77</v>
@@ -9276,21 +9295,21 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>77</v>
+        <v>506</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>77</v>
@@ -9310,10 +9329,10 @@
       <c r="M63" t="s" s="2">
         <v>509</v>
       </c>
-      <c r="N63" s="2"/>
-      <c r="O63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>510</v>
       </c>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>77</v>
       </c>
@@ -9361,13 +9380,13 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>77</v>
@@ -9376,10 +9395,10 @@
         <v>98</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>77</v>
+        <v>511</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>77</v>
@@ -9390,10 +9409,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9416,16 +9435,18 @@
         <v>77</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>157</v>
+        <v>514</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>158</v>
+        <v>515</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>159</v>
+        <v>516</v>
       </c>
       <c r="N64" s="2"/>
-      <c r="O64" s="2"/>
+      <c r="O64" t="s" s="2">
+        <v>517</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>77</v>
       </c>
@@ -9473,7 +9494,7 @@
         <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>160</v>
+        <v>513</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9485,13 +9506,13 @@
         <v>77</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>161</v>
+        <v>518</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>77</v>
@@ -9502,21 +9523,21 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>77</v>
@@ -9528,17 +9549,15 @@
         <v>77</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>132</v>
+        <v>165</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>133</v>
+        <v>166</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>135</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="N65" s="2"/>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>77</v>
@@ -9593,19 +9612,19 @@
         <v>78</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>137</v>
+        <v>77</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>77</v>
@@ -9616,14 +9635,14 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>515</v>
+        <v>145</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -9636,26 +9655,24 @@
         <v>77</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>516</v>
+        <v>172</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>517</v>
+        <v>173</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>141</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>77</v>
       </c>
@@ -9703,7 +9720,7 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>518</v>
+        <v>175</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9721,7 +9738,7 @@
         <v>77</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>129</v>
+        <v>169</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>77</v>
@@ -9732,43 +9749,45 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>77</v>
+        <v>522</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I67" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>520</v>
+        <v>131</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="N67" s="2"/>
+        <v>524</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="O67" t="s" s="2">
-        <v>523</v>
+        <v>149</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>77</v>
@@ -9817,25 +9836,25 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>524</v>
+        <v>129</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>77</v>
@@ -9846,10 +9865,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9872,19 +9891,17 @@
         <v>77</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>287</v>
+        <v>527</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>528</v>
-      </c>
+        <v>529</v>
+      </c>
+      <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>77</v>
@@ -9933,7 +9950,7 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -9951,7 +9968,7 @@
         <v>77</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>77</v>
@@ -9962,10 +9979,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9976,7 +9993,7 @@
         <v>78</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>77</v>
@@ -9988,7 +10005,7 @@
         <v>77</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>532</v>
+        <v>294</v>
       </c>
       <c r="L69" t="s" s="2">
         <v>533</v>
@@ -9996,8 +10013,12 @@
       <c r="M69" t="s" s="2">
         <v>534</v>
       </c>
-      <c r="N69" s="2"/>
-      <c r="O69" s="2"/>
+      <c r="N69" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>536</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>77</v>
       </c>
@@ -10045,13 +10066,13 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>77</v>
@@ -10063,7 +10084,7 @@
         <v>77</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>77</v>
@@ -10074,14 +10095,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>537</v>
+        <v>77</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10100,18 +10121,16 @@
         <v>77</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>507</v>
+        <v>539</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="N70" s="2"/>
-      <c r="O70" t="s" s="2">
-        <v>540</v>
-      </c>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>77</v>
       </c>
@@ -10159,7 +10178,7 @@
         <v>77</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10177,7 +10196,7 @@
         <v>77</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>77</v>
@@ -10188,21 +10207,21 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>77</v>
+        <v>544</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>77</v>
@@ -10214,16 +10233,18 @@
         <v>77</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>157</v>
+        <v>514</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>158</v>
+        <v>545</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>159</v>
+        <v>546</v>
       </c>
       <c r="N71" s="2"/>
-      <c r="O71" s="2"/>
+      <c r="O71" t="s" s="2">
+        <v>547</v>
+      </c>
       <c r="P71" t="s" s="2">
         <v>77</v>
       </c>
@@ -10271,25 +10292,25 @@
         <v>77</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>160</v>
+        <v>543</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>161</v>
+        <v>548</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>77</v>
@@ -10300,21 +10321,21 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>77</v>
@@ -10326,17 +10347,15 @@
         <v>77</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>132</v>
+        <v>165</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>133</v>
+        <v>166</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>135</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="N72" s="2"/>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>77</v>
@@ -10391,19 +10410,19 @@
         <v>78</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>137</v>
+        <v>77</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>77</v>
@@ -10414,14 +10433,14 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>515</v>
+        <v>145</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -10434,26 +10453,24 @@
         <v>77</v>
       </c>
       <c r="I73" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>516</v>
+        <v>172</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>517</v>
+        <v>173</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>141</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>77</v>
       </c>
@@ -10501,7 +10518,7 @@
         <v>77</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>518</v>
+        <v>175</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10519,7 +10536,7 @@
         <v>77</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>129</v>
+        <v>169</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>77</v>
@@ -10530,45 +10547,45 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>546</v>
+        <v>522</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I74" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>182</v>
+        <v>131</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>547</v>
+        <v>523</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>548</v>
+        <v>524</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>549</v>
+        <v>148</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>550</v>
+        <v>149</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>77</v>
@@ -10593,10 +10610,10 @@
         <v>77</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>356</v>
+        <v>77</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>551</v>
+        <v>77</v>
       </c>
       <c r="Z74" t="s" s="2">
         <v>77</v>
@@ -10617,25 +10634,25 @@
         <v>77</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>545</v>
+        <v>525</v>
       </c>
       <c r="AG74" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>541</v>
+        <v>129</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>77</v>
@@ -10653,7 +10670,7 @@
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>77</v>
+        <v>553</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -10672,7 +10689,7 @@
         <v>77</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>553</v>
+        <v>189</v>
       </c>
       <c r="L75" t="s" s="2">
         <v>554</v>
@@ -10680,8 +10697,12 @@
       <c r="M75" t="s" s="2">
         <v>555</v>
       </c>
-      <c r="N75" s="2"/>
-      <c r="O75" s="2"/>
+      <c r="N75" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="O75" t="s" s="2">
+        <v>557</v>
+      </c>
       <c r="P75" t="s" s="2">
         <v>77</v>
       </c>
@@ -10705,10 +10726,10 @@
         <v>77</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>77</v>
+        <v>363</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>77</v>
+        <v>558</v>
       </c>
       <c r="Z75" t="s" s="2">
         <v>77</v>
@@ -10747,7 +10768,7 @@
         <v>77</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>541</v>
+        <v>548</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>77</v>
@@ -10758,10 +10779,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10769,13 +10790,13 @@
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>77</v>
@@ -10784,18 +10805,16 @@
         <v>77</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>507</v>
+        <v>560</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="N76" s="2"/>
-      <c r="O76" t="s" s="2">
-        <v>559</v>
-      </c>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>77</v>
       </c>
@@ -10843,13 +10862,13 @@
         <v>77</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="AG76" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>77</v>
@@ -10861,7 +10880,7 @@
         <v>77</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>541</v>
+        <v>548</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>77</v>
@@ -10872,10 +10891,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10886,10 +10905,10 @@
         <v>78</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="H77" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="I77" t="s" s="2">
         <v>77</v>
@@ -10898,16 +10917,18 @@
         <v>77</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>157</v>
+        <v>514</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>158</v>
+        <v>564</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>159</v>
+        <v>565</v>
       </c>
       <c r="N77" s="2"/>
-      <c r="O77" s="2"/>
+      <c r="O77" t="s" s="2">
+        <v>566</v>
+      </c>
       <c r="P77" t="s" s="2">
         <v>77</v>
       </c>
@@ -10955,25 +10976,25 @@
         <v>77</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>160</v>
+        <v>563</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>161</v>
+        <v>548</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>77</v>
@@ -10984,21 +11005,21 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>77</v>
@@ -11010,17 +11031,15 @@
         <v>77</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>132</v>
+        <v>165</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>133</v>
+        <v>166</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>135</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="N78" s="2"/>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>77</v>
@@ -11075,19 +11094,19 @@
         <v>78</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>137</v>
+        <v>77</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>77</v>
@@ -11098,14 +11117,14 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>515</v>
+        <v>145</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -11118,26 +11137,24 @@
         <v>77</v>
       </c>
       <c r="I79" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>516</v>
+        <v>172</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>517</v>
+        <v>173</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>141</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>77</v>
       </c>
@@ -11185,7 +11202,7 @@
         <v>77</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>518</v>
+        <v>175</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -11203,7 +11220,7 @@
         <v>77</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>129</v>
+        <v>169</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>77</v>
@@ -11214,43 +11231,45 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>546</v>
+        <v>522</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I80" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>182</v>
+        <v>131</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>564</v>
+        <v>523</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="N80" s="2"/>
+        <v>524</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="O80" t="s" s="2">
-        <v>566</v>
+        <v>149</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>77</v>
@@ -11275,10 +11294,10 @@
         <v>77</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>356</v>
+        <v>77</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>567</v>
+        <v>77</v>
       </c>
       <c r="Z80" t="s" s="2">
         <v>77</v>
@@ -11299,25 +11318,25 @@
         <v>77</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>563</v>
+        <v>525</v>
       </c>
       <c r="AG80" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>541</v>
+        <v>129</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>77</v>
@@ -11328,18 +11347,18 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>77</v>
+        <v>553</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="G81" t="s" s="2">
         <v>86</v>
@@ -11354,16 +11373,18 @@
         <v>77</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>157</v>
+        <v>189</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>158</v>
+        <v>571</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>159</v>
+        <v>572</v>
       </c>
       <c r="N81" s="2"/>
-      <c r="O81" s="2"/>
+      <c r="O81" t="s" s="2">
+        <v>573</v>
+      </c>
       <c r="P81" t="s" s="2">
         <v>77</v>
       </c>
@@ -11387,10 +11408,10 @@
         <v>77</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>77</v>
+        <v>363</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>77</v>
+        <v>574</v>
       </c>
       <c r="Z81" t="s" s="2">
         <v>77</v>
@@ -11411,10 +11432,10 @@
         <v>77</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>160</v>
+        <v>570</v>
       </c>
       <c r="AG81" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AH81" t="s" s="2">
         <v>86</v>
@@ -11423,13 +11444,13 @@
         <v>77</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>161</v>
+        <v>548</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>77</v>
@@ -11440,21 +11461,21 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>77</v>
@@ -11466,17 +11487,15 @@
         <v>77</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>132</v>
+        <v>165</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>133</v>
+        <v>166</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>135</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="N82" s="2"/>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>77</v>
@@ -11513,16 +11532,16 @@
         <v>77</v>
       </c>
       <c r="AB82" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AC82" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AD82" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE82" t="s" s="2">
-        <v>167</v>
+        <v>77</v>
       </c>
       <c r="AF82" t="s" s="2">
         <v>168</v>
@@ -11531,19 +11550,19 @@
         <v>78</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>137</v>
+        <v>77</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>77</v>
@@ -11554,14 +11573,14 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>77</v>
+        <v>145</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -11577,23 +11596,21 @@
         <v>77</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>198</v>
+        <v>131</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>199</v>
+        <v>172</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>202</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>77</v>
       </c>
@@ -11629,19 +11646,19 @@
         <v>77</v>
       </c>
       <c r="AB83" t="s" s="2">
-        <v>77</v>
+        <v>134</v>
       </c>
       <c r="AC83" t="s" s="2">
-        <v>77</v>
+        <v>174</v>
       </c>
       <c r="AD83" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>203</v>
+        <v>175</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -11653,27 +11670,27 @@
         <v>77</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>204</v>
+        <v>169</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>205</v>
+        <v>77</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11684,7 +11701,7 @@
         <v>78</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>77</v>
@@ -11693,19 +11710,23 @@
         <v>77</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>157</v>
+        <v>205</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>158</v>
+        <v>206</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="N84" s="2"/>
-      <c r="O84" s="2"/>
+        <v>207</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="O84" t="s" s="2">
+        <v>209</v>
+      </c>
       <c r="P84" t="s" s="2">
         <v>77</v>
       </c>
@@ -11753,50 +11774,50 @@
         <v>77</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>160</v>
+        <v>210</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>161</v>
+        <v>211</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>77</v>
+        <v>212</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>77</v>
@@ -11808,17 +11829,15 @@
         <v>77</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>132</v>
+        <v>165</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>133</v>
+        <v>166</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>135</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="N85" s="2"/>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>77</v>
@@ -11855,16 +11874,16 @@
         <v>77</v>
       </c>
       <c r="AB85" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AC85" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AD85" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE85" t="s" s="2">
-        <v>167</v>
+        <v>77</v>
       </c>
       <c r="AF85" t="s" s="2">
         <v>168</v>
@@ -11873,19 +11892,19 @@
         <v>78</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>137</v>
+        <v>77</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>77</v>
@@ -11896,21 +11915,21 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>77</v>
+        <v>145</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>77</v>
@@ -11919,23 +11938,21 @@
         <v>77</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>100</v>
+        <v>131</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>212</v>
+        <v>172</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>213</v>
+        <v>173</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>215</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>77</v>
       </c>
@@ -11971,51 +11988,51 @@
         <v>77</v>
       </c>
       <c r="AB86" t="s" s="2">
-        <v>77</v>
+        <v>134</v>
       </c>
       <c r="AC86" t="s" s="2">
-        <v>77</v>
+        <v>174</v>
       </c>
       <c r="AD86" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>217</v>
+        <v>175</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>218</v>
+        <v>169</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>219</v>
+        <v>77</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12038,18 +12055,20 @@
         <v>87</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>157</v>
+        <v>100</v>
       </c>
       <c r="L87" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="M87" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="O87" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="M87" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>77</v>
       </c>
@@ -12097,7 +12116,7 @@
         <v>77</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -12115,21 +12134,21 @@
         <v>77</v>
       </c>
       <c r="AL87" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AM87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN87" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="AM87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN87" t="s" s="2">
-        <v>227</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12152,18 +12171,18 @@
         <v>87</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>106</v>
+        <v>165</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="M88" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="M88" t="s" s="2">
+      <c r="N88" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="N88" s="2"/>
-      <c r="O88" t="s" s="2">
-        <v>232</v>
-      </c>
+      <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>77</v>
       </c>
@@ -12187,11 +12206,13 @@
         <v>77</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="Y88" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y88" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="Z88" t="s" s="2">
-        <v>576</v>
+        <v>77</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>77</v>
@@ -12209,7 +12230,7 @@
         <v>77</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -12227,21 +12248,21 @@
         <v>77</v>
       </c>
       <c r="AL88" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="AM88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN88" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="AM88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN88" t="s" s="2">
-        <v>235</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12264,17 +12285,17 @@
         <v>87</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>157</v>
+        <v>106</v>
       </c>
       <c r="L89" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="M89" t="s" s="2">
         <v>238</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>239</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>77</v>
@@ -12299,13 +12320,11 @@
         <v>77</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y89" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="Y89" s="2"/>
       <c r="Z89" t="s" s="2">
-        <v>77</v>
+        <v>583</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>77</v>
@@ -12323,7 +12342,7 @@
         <v>77</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -12341,21 +12360,21 @@
         <v>77</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12378,19 +12397,17 @@
         <v>87</v>
       </c>
       <c r="K90" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="L90" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="N90" s="2"/>
+      <c r="O90" t="s" s="2">
         <v>247</v>
-      </c>
-      <c r="L90" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="M90" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>251</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>77</v>
@@ -12439,7 +12456,7 @@
         <v>77</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -12457,21 +12474,21 @@
         <v>77</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>254</v>
+        <v>251</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12494,19 +12511,19 @@
         <v>87</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>157</v>
+        <v>254</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="N91" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="M91" t="s" s="2">
+      <c r="O91" t="s" s="2">
         <v>258</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>260</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>77</v>
@@ -12516,7 +12533,7 @@
         <v>77</v>
       </c>
       <c r="S91" t="s" s="2">
-        <v>580</v>
+        <v>77</v>
       </c>
       <c r="T91" t="s" s="2">
         <v>77</v>
@@ -12555,7 +12572,7 @@
         <v>77</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -12573,21 +12590,21 @@
         <v>77</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>264</v>
+        <v>261</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12595,7 +12612,7 @@
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="G92" t="s" s="2">
         <v>86</v>
@@ -12607,20 +12624,22 @@
         <v>77</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>582</v>
+        <v>165</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>583</v>
+        <v>264</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="N92" s="2"/>
+        <v>265</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>266</v>
+      </c>
       <c r="O92" t="s" s="2">
-        <v>585</v>
+        <v>267</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>77</v>
@@ -12630,7 +12649,7 @@
         <v>77</v>
       </c>
       <c r="S92" t="s" s="2">
-        <v>77</v>
+        <v>587</v>
       </c>
       <c r="T92" t="s" s="2">
         <v>77</v>
@@ -12657,20 +12676,22 @@
         <v>77</v>
       </c>
       <c r="AB92" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="AC92" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="AD92" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE92" t="s" s="2">
-        <v>587</v>
+        <v>77</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>581</v>
+        <v>269</v>
       </c>
       <c r="AG92" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AH92" t="s" s="2">
         <v>86</v>
@@ -12685,13 +12706,13 @@
         <v>77</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>541</v>
+        <v>270</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>77</v>
+        <v>271</v>
       </c>
     </row>
     <row r="93" hidden="true">
@@ -12699,11 +12720,9 @@
         <v>588</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="C93" t="s" s="2">
-        <v>589</v>
-      </c>
+        <v>588</v>
+      </c>
+      <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
         <v>77</v>
       </c>
@@ -12724,17 +12743,17 @@
         <v>77</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>582</v>
+        <v>589</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>583</v>
+        <v>590</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>584</v>
+        <v>591</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" t="s" s="2">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>77</v>
@@ -12771,19 +12790,17 @@
         <v>77</v>
       </c>
       <c r="AB93" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC93" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>593</v>
+      </c>
+      <c r="AC93" s="2"/>
       <c r="AD93" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE93" t="s" s="2">
-        <v>77</v>
+        <v>594</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>581</v>
+        <v>588</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>86</v>
@@ -12801,17 +12818,133 @@
         <v>77</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>541</v>
+        <v>548</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN93" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="94" hidden="true">
+      <c r="A94" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="B94" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="C94" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="D94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E94" s="2"/>
+      <c r="F94" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="G94" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K94" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="L94" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="M94" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="N94" s="2"/>
+      <c r="O94" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="P94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q94" s="2"/>
+      <c r="R94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF94" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="AG94" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AH94" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ94" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL94" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="AM94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN94" t="s" s="2">
         <v>77</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN93">
+  <autoFilter ref="A1:AN94">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -12821,7 +12954,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI92">
+  <conditionalFormatting sqref="A2:AI93">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/branches/master/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/master/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T20:00:55+00:00</t>
+    <t>2023-05-08T21:08:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/master/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T19:02:34+00:00</t>
+    <t>2023-05-11T19:57:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/master/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T19:57:24+00:00</t>
+    <t>2023-05-11T20:42:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/master/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T20:42:55+00:00</t>
+    <t>2023-05-12T08:27:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/master/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T08:27:31+00:00</t>
+    <t>2023-05-12T10:53:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/master/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:53:52+00:00</t>
+    <t>2023-05-12T13:58:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/master/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T13:58:20+00:00</t>
+    <t>2023-05-23T09:20:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
